--- a/samples/monthly_report/월간실적_품질팀.xlsx
+++ b/samples/monthly_report/월간실적_품질팀.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -54,7 +51,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -432,49 +429,69 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>관리항목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dept</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>년월</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>실적치</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>목표치</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>관리항목</t>
+          <t>고객불량률(ppm)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dept</t>
+          <t>품질팀</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>년월</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>실적치</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>목표치</t>
-        </is>
+          <t>2026년 8월</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>특이사항</t>
+          <t>목표 재검토 필요</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>고객불량률(ppm)</t>
+          <t>수입검사건수</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,10 +505,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50.4</v>
+        <v>432.4</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -502,7 +519,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>수입검사건수</t>
+          <t>수입검사불합격건수</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -516,10 +533,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>432.4</v>
+        <v>5.1</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -530,7 +547,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>수입검사불합격건수</t>
+          <t>시정조치완료율(%)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -543,22 +560,24 @@
           <t>2026년 8월</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>5.1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3건</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>목표 재검토 필요</t>
+          <t>전월 대비 개선</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>시정조치완료율(%)</t>
+          <t>내부심사건수</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,24 +590,17 @@
           <t>2026년 8월</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3건</t>
-        </is>
+      <c r="D6" t="n">
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>전월 대비 개선</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>내부심사건수</t>
+          <t>계측기교정완료율(%)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -602,21 +614,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>104.7</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>계측기교정완료율(%)</t>
+          <t>품질비용(백만원)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>품질팀</t>
+          <t>QA팀</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -625,21 +637,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>104.7</v>
+        <v>39.1</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>목표 재검토 필요</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>품질비용(백만원)</t>
+          <t>협력사평가건수</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>QA팀</t>
+          <t>품질팀</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -648,21 +665,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>39.1</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>목표 재검토 필요</t>
+          <t>전월 대비 개선</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>협력사평가건수</t>
+          <t>신뢰성시험건수</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -676,21 +693,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>전월 대비 개선</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>신뢰성시험건수</t>
+          <t>고객감사대응건수</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -704,21 +716,21 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>1.1</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>고객감사대응건수</t>
+          <t>에너지사용량(MWh)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>품질팀</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,32 +739,9 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1</v>
+        <v>179.8</v>
       </c>
       <c r="E12" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>에너지사용량(MWh)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>생산팀</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026년 8월</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>179.8</v>
-      </c>
-      <c r="E13" t="n">
         <v>180</v>
       </c>
     </row>
